--- a/scanner_output.xlsx
+++ b/scanner_output.xlsx
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="CH2" t="n">
-        <v>252.08</v>
+        <v>262.02</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>252.08</v>
+        <v>262.02</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:05-04:00</t>
+          <t>2026-08-01 00:22:01-04:00</t>
         </is>
       </c>
       <c r="CM2" t="b">
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="CH3" t="n">
-        <v>252.1</v>
+        <v>262.03</v>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="CJ3" t="n">
-        <v>252.1</v>
+        <v>262.03</v>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:05-04:00</t>
+          <t>2026-08-01 00:22:02-04:00</t>
         </is>
       </c>
       <c r="CM3" t="b">
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="CH4" t="n">
-        <v>252.1</v>
+        <v>262.04</v>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="CJ4" t="n">
-        <v>252.1</v>
+        <v>262.04</v>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:06-04:00</t>
+          <t>2026-08-01 00:22:02-04:00</t>
         </is>
       </c>
       <c r="CM4" t="b">
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="CH5" t="n">
-        <v>252.11</v>
+        <v>262.05</v>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="CJ5" t="n">
-        <v>252.11</v>
+        <v>262.05</v>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:06-04:00</t>
+          <t>2026-08-01 00:22:03-04:00</t>
         </is>
       </c>
       <c r="CM5" t="b">
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="CH6" t="n">
-        <v>252.12</v>
+        <v>262.07</v>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="CJ6" t="n">
-        <v>252.12</v>
+        <v>262.07</v>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:07-04:00</t>
+          <t>2026-08-01 00:22:04-04:00</t>
         </is>
       </c>
       <c r="CM6" t="b">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="CH7" t="n">
-        <v>252.13</v>
+        <v>262.08</v>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="CJ7" t="n">
-        <v>252.13</v>
+        <v>262.08</v>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:07-04:00</t>
+          <t>2026-08-01 00:22:04-04:00</t>
         </is>
       </c>
       <c r="CM7" t="b">
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="CH8" t="n">
-        <v>252.18</v>
+        <v>262.09</v>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="CJ8" t="n">
-        <v>252.18</v>
+        <v>262.09</v>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:10-04:00</t>
+          <t>2026-08-01 00:22:05-04:00</t>
         </is>
       </c>
       <c r="CM8" t="b">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="CH9" t="n">
-        <v>252.19</v>
+        <v>262.1</v>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="CJ9" t="n">
-        <v>252.19</v>
+        <v>262.1</v>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:11-04:00</t>
+          <t>2026-08-01 00:22:06-04:00</t>
         </is>
       </c>
       <c r="CM9" t="b">
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="CH10" t="n">
-        <v>252.19</v>
+        <v>262.11</v>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="CJ10" t="n">
-        <v>252.19</v>
+        <v>262.11</v>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:11-04:00</t>
+          <t>2026-08-01 00:22:06-04:00</t>
         </is>
       </c>
       <c r="CM10" t="b">
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="CH11" t="n">
-        <v>252.2</v>
+        <v>262.12</v>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="CJ11" t="n">
-        <v>252.2</v>
+        <v>262.12</v>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:12-04:00</t>
+          <t>2026-08-01 00:22:07-04:00</t>
         </is>
       </c>
       <c r="CM11" t="b">
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="CH12" t="n">
-        <v>252.21</v>
+        <v>262.13</v>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="CJ12" t="n">
-        <v>252.21</v>
+        <v>262.13</v>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:12-04:00</t>
+          <t>2026-08-01 00:22:08-04:00</t>
         </is>
       </c>
       <c r="CM12" t="b">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="CH13" t="n">
-        <v>252.22</v>
+        <v>262.15</v>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="CJ13" t="n">
-        <v>252.22</v>
+        <v>262.15</v>
       </c>
       <c r="CK13" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:13-04:00</t>
+          <t>2026-08-01 00:22:08-04:00</t>
         </is>
       </c>
       <c r="CM13" t="b">
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="CH14" t="n">
-        <v>252.22</v>
+        <v>262.16</v>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="CJ14" t="n">
-        <v>252.22</v>
+        <v>262.16</v>
       </c>
       <c r="CK14" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:13-04:00</t>
+          <t>2026-08-01 00:22:09-04:00</t>
         </is>
       </c>
       <c r="CM14" t="b">
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="CH15" t="n">
-        <v>252.23</v>
+        <v>262.17</v>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="CJ15" t="n">
-        <v>252.23</v>
+        <v>262.17</v>
       </c>
       <c r="CK15" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:14-04:00</t>
+          <t>2026-08-01 00:22:10-04:00</t>
         </is>
       </c>
       <c r="CM15" t="b">
@@ -13005,7 +13005,7 @@
         </is>
       </c>
       <c r="CH16" t="n">
-        <v>252.24</v>
+        <v>262.18</v>
       </c>
       <c r="CI16" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="CJ16" t="n">
-        <v>252.24</v>
+        <v>262.18</v>
       </c>
       <c r="CK16" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:14-04:00</t>
+          <t>2026-08-01 00:22:10-04:00</t>
         </is>
       </c>
       <c r="CM16" t="b">
@@ -13761,7 +13761,7 @@
         </is>
       </c>
       <c r="CH17" t="n">
-        <v>252.25</v>
+        <v>262.19</v>
       </c>
       <c r="CI17" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="CJ17" t="n">
-        <v>252.25</v>
+        <v>262.19</v>
       </c>
       <c r="CK17" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:14-04:00</t>
+          <t>2026-08-01 00:22:11-04:00</t>
         </is>
       </c>
       <c r="CM17" t="b">
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="CH18" t="n">
-        <v>252.26</v>
+        <v>262.2</v>
       </c>
       <c r="CI18" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         </is>
       </c>
       <c r="CJ18" t="n">
-        <v>252.26</v>
+        <v>262.2</v>
       </c>
       <c r="CK18" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:15-04:00</t>
+          <t>2026-08-01 00:22:12-04:00</t>
         </is>
       </c>
       <c r="CM18" t="b">
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="CH19" t="n">
-        <v>252.26</v>
+        <v>262.21</v>
       </c>
       <c r="CI19" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="CJ19" t="n">
-        <v>252.26</v>
+        <v>262.21</v>
       </c>
       <c r="CK19" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:15-04:00</t>
+          <t>2026-08-01 00:22:12-04:00</t>
         </is>
       </c>
       <c r="CM19" t="b">
@@ -16077,7 +16077,7 @@
         </is>
       </c>
       <c r="CH20" t="n">
-        <v>252.27</v>
+        <v>262.23</v>
       </c>
       <c r="CI20" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="CJ20" t="n">
-        <v>252.27</v>
+        <v>262.23</v>
       </c>
       <c r="CK20" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:16-04:00</t>
+          <t>2026-08-01 00:22:13-04:00</t>
         </is>
       </c>
       <c r="CM20" t="b">
@@ -16849,7 +16849,7 @@
         </is>
       </c>
       <c r="CH21" t="n">
-        <v>252.28</v>
+        <v>262.24</v>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         </is>
       </c>
       <c r="CJ21" t="n">
-        <v>252.28</v>
+        <v>262.24</v>
       </c>
       <c r="CK21" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:16-04:00</t>
+          <t>2026-08-01 00:22:14-04:00</t>
         </is>
       </c>
       <c r="CM21" t="b">
@@ -17619,7 +17619,7 @@
         </is>
       </c>
       <c r="CH22" t="n">
-        <v>252.29</v>
+        <v>262.26</v>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         </is>
       </c>
       <c r="CJ22" t="n">
-        <v>252.29</v>
+        <v>262.26</v>
       </c>
       <c r="CK22" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:17-04:00</t>
+          <t>2026-08-01 00:22:15-04:00</t>
         </is>
       </c>
       <c r="CM22" t="b">
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="CH23" t="n">
-        <v>252.29</v>
+        <v>262.27</v>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         </is>
       </c>
       <c r="CJ23" t="n">
-        <v>252.29</v>
+        <v>262.27</v>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:17-04:00</t>
+          <t>2026-08-01 00:22:16-04:00</t>
         </is>
       </c>
       <c r="CM23" t="b">
@@ -19163,7 +19163,7 @@
         </is>
       </c>
       <c r="CH24" t="n">
-        <v>252.3</v>
+        <v>262.28</v>
       </c>
       <c r="CI24" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="CJ24" t="n">
-        <v>252.3</v>
+        <v>262.28</v>
       </c>
       <c r="CK24" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:18-04:00</t>
+          <t>2026-08-01 00:22:16-04:00</t>
         </is>
       </c>
       <c r="CM24" t="b">
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="CH25" t="n">
-        <v>252.31</v>
+        <v>262.43</v>
       </c>
       <c r="CI25" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         </is>
       </c>
       <c r="CJ25" t="n">
-        <v>252.31</v>
+        <v>262.43</v>
       </c>
       <c r="CK25" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:18-04:00</t>
+          <t>2026-08-01 00:22:26-04:00</t>
         </is>
       </c>
       <c r="CM25" t="b">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="CH26" t="n">
-        <v>297.32</v>
+        <v>307.45</v>
       </c>
       <c r="CI26" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         </is>
       </c>
       <c r="CJ26" t="n">
-        <v>297.32</v>
+        <v>307.45</v>
       </c>
       <c r="CK26" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:19-04:00</t>
+          <t>2026-08-01 00:22:26-04:00</t>
         </is>
       </c>
       <c r="CM26" t="b">
@@ -21479,7 +21479,7 @@
         </is>
       </c>
       <c r="CH27" t="n">
-        <v>252.32</v>
+        <v>262.46</v>
       </c>
       <c r="CI27" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         </is>
       </c>
       <c r="CJ27" t="n">
-        <v>252.32</v>
+        <v>262.46</v>
       </c>
       <c r="CK27" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:19-04:00</t>
+          <t>2026-08-01 00:22:27-04:00</t>
         </is>
       </c>
       <c r="CM27" t="b">

--- a/scanner_output.xlsx
+++ b/scanner_output.xlsx
@@ -1228,7 +1228,7 @@
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ2" t="b">
@@ -1556,7 +1556,7 @@
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ3" t="b">
@@ -1884,7 +1884,7 @@
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ4" t="b">
@@ -2212,7 +2212,7 @@
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ5" t="b">
@@ -2540,7 +2540,7 @@
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ6" t="b">
@@ -2868,7 +2868,7 @@
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ7" t="b">
@@ -3196,7 +3196,7 @@
       <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ8" t="b">
@@ -3524,7 +3524,7 @@
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ9" t="b">
@@ -3852,7 +3852,7 @@
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ10" t="b">
@@ -4180,7 +4180,7 @@
       <c r="BO11" t="inlineStr"/>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ11" t="b">
@@ -4508,7 +4508,7 @@
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ12" t="b">
@@ -4836,7 +4836,7 @@
       <c r="BO13" t="inlineStr"/>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ13" t="b">
@@ -5164,7 +5164,7 @@
       <c r="BO14" t="inlineStr"/>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ14" t="b">
@@ -5492,7 +5492,7 @@
       <c r="BO15" t="inlineStr"/>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ15" t="b">
@@ -5820,7 +5820,7 @@
       <c r="BO16" t="inlineStr"/>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ16" t="b">
@@ -6148,7 +6148,7 @@
       <c r="BO17" t="inlineStr"/>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ17" t="b">
@@ -6476,7 +6476,7 @@
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ18" t="b">
@@ -6804,7 +6804,7 @@
       <c r="BO19" t="inlineStr"/>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ19" t="b">
@@ -7132,7 +7132,7 @@
       <c r="BO20" t="inlineStr"/>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ20" t="b">
@@ -7460,7 +7460,7 @@
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ21" t="b">
@@ -7788,7 +7788,7 @@
       <c r="BO22" t="inlineStr"/>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ22" t="b">
@@ -8116,7 +8116,7 @@
       <c r="BO23" t="inlineStr"/>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ23" t="b">
@@ -8444,7 +8444,7 @@
       <c r="BO24" t="inlineStr"/>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ24" t="b">
@@ -8772,7 +8772,7 @@
       <c r="BO25" t="inlineStr"/>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ25" t="b">
@@ -9100,7 +9100,7 @@
       <c r="BO26" t="inlineStr"/>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ26" t="b">
@@ -9428,7 +9428,7 @@
       <c r="BO27" t="inlineStr"/>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ27" t="b">

--- a/scanner_output.xlsx
+++ b/scanner_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DX27"/>
+  <dimension ref="A1:DY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,80 +991,85 @@
       </c>
       <c r="DI1" s="1" t="inlineStr">
         <is>
+          <t>Option Premium % of Notional</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
           <t>Candidate Rank</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>Holding Profile</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>Scanner Recommendation</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>Execution Eligibility</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>Execution Outcome</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>Execution Reason</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>Trade Status</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>Telegram Status</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>Telegram Reason</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>Telegram Eligibility</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>Telegram Block Reason</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>Telegram Sent</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>Telegram Alert Score</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>Telegram Error Type</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>Telegram Error Reason</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>Telegram Stage</t>
         </is>
@@ -1228,7 +1233,7 @@
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ2" t="b">
@@ -1327,72 +1332,73 @@
       <c r="DD2" t="inlineStr"/>
       <c r="DE2" t="inlineStr"/>
       <c r="DF2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="n">
         <v>1</v>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr"/>
-      <c r="DO2" t="inlineStr">
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="inlineStr"/>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
       <c r="DV2" t="inlineStr"/>
       <c r="DW2" t="inlineStr"/>
-      <c r="DX2" t="inlineStr">
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -1556,7 +1562,7 @@
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ3" t="b">
@@ -1655,72 +1661,73 @@
       <c r="DD3" t="inlineStr"/>
       <c r="DE3" t="inlineStr"/>
       <c r="DF3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI3" t="n">
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="n">
         <v>2</v>
       </c>
-      <c r="DJ3" t="inlineStr">
+      <c r="DK3" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK3" t="inlineStr">
+      <c r="DL3" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL3" t="inlineStr">
+      <c r="DM3" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM3" t="inlineStr">
+      <c r="DN3" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN3" t="inlineStr"/>
-      <c r="DO3" t="inlineStr">
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP3" t="inlineStr">
+      <c r="DQ3" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ3" t="inlineStr">
+      <c r="DR3" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR3" t="inlineStr">
+      <c r="DS3" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS3" t="inlineStr">
+      <c r="DT3" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU3" t="inlineStr"/>
+      <c r="DU3" t="b">
+        <v>0</v>
+      </c>
       <c r="DV3" t="inlineStr"/>
       <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="inlineStr">
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -1884,7 +1891,7 @@
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ4" t="b">
@@ -1983,72 +1990,73 @@
       <c r="DD4" t="inlineStr"/>
       <c r="DE4" t="inlineStr"/>
       <c r="DF4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI4" t="n">
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="n">
         <v>3</v>
       </c>
-      <c r="DJ4" t="inlineStr">
+      <c r="DK4" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK4" t="inlineStr">
+      <c r="DL4" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL4" t="inlineStr">
+      <c r="DM4" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM4" t="inlineStr">
+      <c r="DN4" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN4" t="inlineStr"/>
-      <c r="DO4" t="inlineStr">
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP4" t="inlineStr">
+      <c r="DQ4" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ4" t="inlineStr">
+      <c r="DR4" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR4" t="inlineStr">
+      <c r="DS4" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS4" t="inlineStr">
+      <c r="DT4" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU4" t="inlineStr"/>
+      <c r="DU4" t="b">
+        <v>0</v>
+      </c>
       <c r="DV4" t="inlineStr"/>
       <c r="DW4" t="inlineStr"/>
-      <c r="DX4" t="inlineStr">
+      <c r="DX4" t="inlineStr"/>
+      <c r="DY4" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -2212,7 +2220,7 @@
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ5" t="b">
@@ -2311,72 +2319,73 @@
       <c r="DD5" t="inlineStr"/>
       <c r="DE5" t="inlineStr"/>
       <c r="DF5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI5" t="n">
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="n">
         <v>4</v>
       </c>
-      <c r="DJ5" t="inlineStr">
+      <c r="DK5" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK5" t="inlineStr">
+      <c r="DL5" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL5" t="inlineStr">
+      <c r="DM5" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM5" t="inlineStr">
+      <c r="DN5" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN5" t="inlineStr"/>
-      <c r="DO5" t="inlineStr">
+      <c r="DO5" t="inlineStr"/>
+      <c r="DP5" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP5" t="inlineStr">
+      <c r="DQ5" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ5" t="inlineStr">
+      <c r="DR5" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR5" t="inlineStr">
+      <c r="DS5" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS5" t="inlineStr">
+      <c r="DT5" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT5" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU5" t="inlineStr"/>
+      <c r="DU5" t="b">
+        <v>0</v>
+      </c>
       <c r="DV5" t="inlineStr"/>
       <c r="DW5" t="inlineStr"/>
-      <c r="DX5" t="inlineStr">
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -2540,7 +2549,7 @@
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ6" t="b">
@@ -2639,72 +2648,73 @@
       <c r="DD6" t="inlineStr"/>
       <c r="DE6" t="inlineStr"/>
       <c r="DF6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI6" t="n">
+      <c r="DI6" t="inlineStr"/>
+      <c r="DJ6" t="n">
         <v>5</v>
       </c>
-      <c r="DJ6" t="inlineStr">
+      <c r="DK6" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK6" t="inlineStr">
+      <c r="DL6" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL6" t="inlineStr">
+      <c r="DM6" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM6" t="inlineStr">
+      <c r="DN6" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN6" t="inlineStr"/>
-      <c r="DO6" t="inlineStr">
+      <c r="DO6" t="inlineStr"/>
+      <c r="DP6" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP6" t="inlineStr">
+      <c r="DQ6" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ6" t="inlineStr">
+      <c r="DR6" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR6" t="inlineStr">
+      <c r="DS6" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS6" t="inlineStr">
+      <c r="DT6" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT6" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU6" t="inlineStr"/>
+      <c r="DU6" t="b">
+        <v>0</v>
+      </c>
       <c r="DV6" t="inlineStr"/>
       <c r="DW6" t="inlineStr"/>
-      <c r="DX6" t="inlineStr">
+      <c r="DX6" t="inlineStr"/>
+      <c r="DY6" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -2868,7 +2878,7 @@
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ7" t="b">
@@ -2967,72 +2977,73 @@
       <c r="DD7" t="inlineStr"/>
       <c r="DE7" t="inlineStr"/>
       <c r="DF7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI7" t="n">
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="n">
         <v>6</v>
       </c>
-      <c r="DJ7" t="inlineStr">
+      <c r="DK7" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK7" t="inlineStr">
+      <c r="DL7" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL7" t="inlineStr">
+      <c r="DM7" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM7" t="inlineStr">
+      <c r="DN7" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN7" t="inlineStr"/>
-      <c r="DO7" t="inlineStr">
+      <c r="DO7" t="inlineStr"/>
+      <c r="DP7" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP7" t="inlineStr">
+      <c r="DQ7" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ7" t="inlineStr">
+      <c r="DR7" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR7" t="inlineStr">
+      <c r="DS7" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS7" t="inlineStr">
+      <c r="DT7" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT7" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU7" t="inlineStr"/>
+      <c r="DU7" t="b">
+        <v>0</v>
+      </c>
       <c r="DV7" t="inlineStr"/>
       <c r="DW7" t="inlineStr"/>
-      <c r="DX7" t="inlineStr">
+      <c r="DX7" t="inlineStr"/>
+      <c r="DY7" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -3196,7 +3207,7 @@
       <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ8" t="b">
@@ -3295,72 +3306,73 @@
       <c r="DD8" t="inlineStr"/>
       <c r="DE8" t="inlineStr"/>
       <c r="DF8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI8" t="n">
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="n">
         <v>7</v>
       </c>
-      <c r="DJ8" t="inlineStr">
+      <c r="DK8" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK8" t="inlineStr">
+      <c r="DL8" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL8" t="inlineStr">
+      <c r="DM8" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM8" t="inlineStr">
+      <c r="DN8" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN8" t="inlineStr"/>
-      <c r="DO8" t="inlineStr">
+      <c r="DO8" t="inlineStr"/>
+      <c r="DP8" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP8" t="inlineStr">
+      <c r="DQ8" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ8" t="inlineStr">
+      <c r="DR8" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR8" t="inlineStr">
+      <c r="DS8" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS8" t="inlineStr">
+      <c r="DT8" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT8" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU8" t="inlineStr"/>
+      <c r="DU8" t="b">
+        <v>0</v>
+      </c>
       <c r="DV8" t="inlineStr"/>
       <c r="DW8" t="inlineStr"/>
-      <c r="DX8" t="inlineStr">
+      <c r="DX8" t="inlineStr"/>
+      <c r="DY8" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -3369,7 +3381,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3524,7 +3536,7 @@
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ9" t="b">
@@ -3623,72 +3635,73 @@
       <c r="DD9" t="inlineStr"/>
       <c r="DE9" t="inlineStr"/>
       <c r="DF9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI9" t="n">
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="n">
         <v>8</v>
       </c>
-      <c r="DJ9" t="inlineStr">
+      <c r="DK9" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK9" t="inlineStr">
+      <c r="DL9" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL9" t="inlineStr">
+      <c r="DM9" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM9" t="inlineStr">
+      <c r="DN9" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN9" t="inlineStr"/>
-      <c r="DO9" t="inlineStr">
+      <c r="DO9" t="inlineStr"/>
+      <c r="DP9" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP9" t="inlineStr">
+      <c r="DQ9" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ9" t="inlineStr">
+      <c r="DR9" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR9" t="inlineStr">
+      <c r="DS9" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS9" t="inlineStr">
+      <c r="DT9" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT9" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU9" t="inlineStr"/>
+      <c r="DU9" t="b">
+        <v>0</v>
+      </c>
       <c r="DV9" t="inlineStr"/>
       <c r="DW9" t="inlineStr"/>
-      <c r="DX9" t="inlineStr">
+      <c r="DX9" t="inlineStr"/>
+      <c r="DY9" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -3697,7 +3710,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3852,7 +3865,7 @@
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ10" t="b">
@@ -3951,72 +3964,73 @@
       <c r="DD10" t="inlineStr"/>
       <c r="DE10" t="inlineStr"/>
       <c r="DF10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI10" t="n">
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="n">
         <v>9</v>
       </c>
-      <c r="DJ10" t="inlineStr">
+      <c r="DK10" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK10" t="inlineStr">
+      <c r="DL10" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL10" t="inlineStr">
+      <c r="DM10" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM10" t="inlineStr">
+      <c r="DN10" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN10" t="inlineStr"/>
-      <c r="DO10" t="inlineStr">
+      <c r="DO10" t="inlineStr"/>
+      <c r="DP10" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP10" t="inlineStr">
+      <c r="DQ10" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ10" t="inlineStr">
+      <c r="DR10" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR10" t="inlineStr">
+      <c r="DS10" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS10" t="inlineStr">
+      <c r="DT10" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT10" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU10" t="inlineStr"/>
+      <c r="DU10" t="b">
+        <v>0</v>
+      </c>
       <c r="DV10" t="inlineStr"/>
       <c r="DW10" t="inlineStr"/>
-      <c r="DX10" t="inlineStr">
+      <c r="DX10" t="inlineStr"/>
+      <c r="DY10" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -4025,7 +4039,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4180,7 +4194,7 @@
       <c r="BO11" t="inlineStr"/>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ11" t="b">
@@ -4279,72 +4293,73 @@
       <c r="DD11" t="inlineStr"/>
       <c r="DE11" t="inlineStr"/>
       <c r="DF11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH11" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI11" t="n">
+      <c r="DI11" t="inlineStr"/>
+      <c r="DJ11" t="n">
         <v>10</v>
       </c>
-      <c r="DJ11" t="inlineStr">
+      <c r="DK11" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK11" t="inlineStr">
+      <c r="DL11" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL11" t="inlineStr">
+      <c r="DM11" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM11" t="inlineStr">
+      <c r="DN11" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN11" t="inlineStr"/>
-      <c r="DO11" t="inlineStr">
+      <c r="DO11" t="inlineStr"/>
+      <c r="DP11" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP11" t="inlineStr">
+      <c r="DQ11" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ11" t="inlineStr">
+      <c r="DR11" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR11" t="inlineStr">
+      <c r="DS11" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS11" t="inlineStr">
+      <c r="DT11" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT11" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU11" t="inlineStr"/>
+      <c r="DU11" t="b">
+        <v>0</v>
+      </c>
       <c r="DV11" t="inlineStr"/>
       <c r="DW11" t="inlineStr"/>
-      <c r="DX11" t="inlineStr">
+      <c r="DX11" t="inlineStr"/>
+      <c r="DY11" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -4353,7 +4368,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4508,7 +4523,7 @@
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ12" t="b">
@@ -4607,72 +4622,73 @@
       <c r="DD12" t="inlineStr"/>
       <c r="DE12" t="inlineStr"/>
       <c r="DF12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH12" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI12" t="n">
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="n">
         <v>11</v>
       </c>
-      <c r="DJ12" t="inlineStr">
+      <c r="DK12" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK12" t="inlineStr">
+      <c r="DL12" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL12" t="inlineStr">
+      <c r="DM12" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM12" t="inlineStr">
+      <c r="DN12" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN12" t="inlineStr"/>
-      <c r="DO12" t="inlineStr">
+      <c r="DO12" t="inlineStr"/>
+      <c r="DP12" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP12" t="inlineStr">
+      <c r="DQ12" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ12" t="inlineStr">
+      <c r="DR12" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR12" t="inlineStr">
+      <c r="DS12" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS12" t="inlineStr">
+      <c r="DT12" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT12" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU12" t="inlineStr"/>
+      <c r="DU12" t="b">
+        <v>0</v>
+      </c>
       <c r="DV12" t="inlineStr"/>
       <c r="DW12" t="inlineStr"/>
-      <c r="DX12" t="inlineStr">
+      <c r="DX12" t="inlineStr"/>
+      <c r="DY12" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -4681,7 +4697,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4836,7 +4852,7 @@
       <c r="BO13" t="inlineStr"/>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ13" t="b">
@@ -4935,72 +4951,73 @@
       <c r="DD13" t="inlineStr"/>
       <c r="DE13" t="inlineStr"/>
       <c r="DF13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH13" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI13" t="n">
+      <c r="DI13" t="inlineStr"/>
+      <c r="DJ13" t="n">
         <v>12</v>
       </c>
-      <c r="DJ13" t="inlineStr">
+      <c r="DK13" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK13" t="inlineStr">
+      <c r="DL13" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL13" t="inlineStr">
+      <c r="DM13" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM13" t="inlineStr">
+      <c r="DN13" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN13" t="inlineStr"/>
-      <c r="DO13" t="inlineStr">
+      <c r="DO13" t="inlineStr"/>
+      <c r="DP13" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP13" t="inlineStr">
+      <c r="DQ13" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ13" t="inlineStr">
+      <c r="DR13" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR13" t="inlineStr">
+      <c r="DS13" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS13" t="inlineStr">
+      <c r="DT13" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT13" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU13" t="inlineStr"/>
+      <c r="DU13" t="b">
+        <v>0</v>
+      </c>
       <c r="DV13" t="inlineStr"/>
       <c r="DW13" t="inlineStr"/>
-      <c r="DX13" t="inlineStr">
+      <c r="DX13" t="inlineStr"/>
+      <c r="DY13" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -5009,7 +5026,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5164,7 +5181,7 @@
       <c r="BO14" t="inlineStr"/>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ14" t="b">
@@ -5263,72 +5280,73 @@
       <c r="DD14" t="inlineStr"/>
       <c r="DE14" t="inlineStr"/>
       <c r="DF14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH14" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI14" t="n">
+      <c r="DI14" t="inlineStr"/>
+      <c r="DJ14" t="n">
         <v>13</v>
       </c>
-      <c r="DJ14" t="inlineStr">
+      <c r="DK14" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK14" t="inlineStr">
+      <c r="DL14" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL14" t="inlineStr">
+      <c r="DM14" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM14" t="inlineStr">
+      <c r="DN14" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN14" t="inlineStr"/>
-      <c r="DO14" t="inlineStr">
+      <c r="DO14" t="inlineStr"/>
+      <c r="DP14" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP14" t="inlineStr">
+      <c r="DQ14" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ14" t="inlineStr">
+      <c r="DR14" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR14" t="inlineStr">
+      <c r="DS14" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS14" t="inlineStr">
+      <c r="DT14" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT14" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU14" t="inlineStr"/>
+      <c r="DU14" t="b">
+        <v>0</v>
+      </c>
       <c r="DV14" t="inlineStr"/>
       <c r="DW14" t="inlineStr"/>
-      <c r="DX14" t="inlineStr">
+      <c r="DX14" t="inlineStr"/>
+      <c r="DY14" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -5337,7 +5355,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5492,7 +5510,7 @@
       <c r="BO15" t="inlineStr"/>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ15" t="b">
@@ -5591,72 +5609,73 @@
       <c r="DD15" t="inlineStr"/>
       <c r="DE15" t="inlineStr"/>
       <c r="DF15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH15" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI15" t="n">
+      <c r="DI15" t="inlineStr"/>
+      <c r="DJ15" t="n">
         <v>14</v>
       </c>
-      <c r="DJ15" t="inlineStr">
+      <c r="DK15" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK15" t="inlineStr">
+      <c r="DL15" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL15" t="inlineStr">
+      <c r="DM15" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM15" t="inlineStr">
+      <c r="DN15" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN15" t="inlineStr"/>
-      <c r="DO15" t="inlineStr">
+      <c r="DO15" t="inlineStr"/>
+      <c r="DP15" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP15" t="inlineStr">
+      <c r="DQ15" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ15" t="inlineStr">
+      <c r="DR15" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR15" t="inlineStr">
+      <c r="DS15" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS15" t="inlineStr">
+      <c r="DT15" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT15" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU15" t="inlineStr"/>
+      <c r="DU15" t="b">
+        <v>0</v>
+      </c>
       <c r="DV15" t="inlineStr"/>
       <c r="DW15" t="inlineStr"/>
-      <c r="DX15" t="inlineStr">
+      <c r="DX15" t="inlineStr"/>
+      <c r="DY15" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -5665,7 +5684,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5820,7 +5839,7 @@
       <c r="BO16" t="inlineStr"/>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ16" t="b">
@@ -5919,72 +5938,73 @@
       <c r="DD16" t="inlineStr"/>
       <c r="DE16" t="inlineStr"/>
       <c r="DF16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH16" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI16" t="n">
+      <c r="DI16" t="inlineStr"/>
+      <c r="DJ16" t="n">
         <v>15</v>
       </c>
-      <c r="DJ16" t="inlineStr">
+      <c r="DK16" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK16" t="inlineStr">
+      <c r="DL16" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL16" t="inlineStr">
+      <c r="DM16" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM16" t="inlineStr">
+      <c r="DN16" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN16" t="inlineStr"/>
-      <c r="DO16" t="inlineStr">
+      <c r="DO16" t="inlineStr"/>
+      <c r="DP16" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP16" t="inlineStr">
+      <c r="DQ16" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ16" t="inlineStr">
+      <c r="DR16" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR16" t="inlineStr">
+      <c r="DS16" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS16" t="inlineStr">
+      <c r="DT16" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT16" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU16" t="inlineStr"/>
+      <c r="DU16" t="b">
+        <v>0</v>
+      </c>
       <c r="DV16" t="inlineStr"/>
       <c r="DW16" t="inlineStr"/>
-      <c r="DX16" t="inlineStr">
+      <c r="DX16" t="inlineStr"/>
+      <c r="DY16" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -5993,7 +6013,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6148,7 +6168,7 @@
       <c r="BO17" t="inlineStr"/>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ17" t="b">
@@ -6247,72 +6267,73 @@
       <c r="DD17" t="inlineStr"/>
       <c r="DE17" t="inlineStr"/>
       <c r="DF17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH17" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI17" t="n">
+      <c r="DI17" t="inlineStr"/>
+      <c r="DJ17" t="n">
         <v>16</v>
       </c>
-      <c r="DJ17" t="inlineStr">
+      <c r="DK17" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK17" t="inlineStr">
+      <c r="DL17" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL17" t="inlineStr">
+      <c r="DM17" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM17" t="inlineStr">
+      <c r="DN17" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN17" t="inlineStr"/>
-      <c r="DO17" t="inlineStr">
+      <c r="DO17" t="inlineStr"/>
+      <c r="DP17" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP17" t="inlineStr">
+      <c r="DQ17" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ17" t="inlineStr">
+      <c r="DR17" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR17" t="inlineStr">
+      <c r="DS17" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS17" t="inlineStr">
+      <c r="DT17" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT17" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU17" t="inlineStr"/>
+      <c r="DU17" t="b">
+        <v>0</v>
+      </c>
       <c r="DV17" t="inlineStr"/>
       <c r="DW17" t="inlineStr"/>
-      <c r="DX17" t="inlineStr">
+      <c r="DX17" t="inlineStr"/>
+      <c r="DY17" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -6321,7 +6342,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6476,7 +6497,7 @@
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ18" t="b">
@@ -6575,72 +6596,73 @@
       <c r="DD18" t="inlineStr"/>
       <c r="DE18" t="inlineStr"/>
       <c r="DF18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH18" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI18" t="n">
+      <c r="DI18" t="inlineStr"/>
+      <c r="DJ18" t="n">
         <v>17</v>
       </c>
-      <c r="DJ18" t="inlineStr">
+      <c r="DK18" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK18" t="inlineStr">
+      <c r="DL18" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL18" t="inlineStr">
+      <c r="DM18" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM18" t="inlineStr">
+      <c r="DN18" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN18" t="inlineStr"/>
-      <c r="DO18" t="inlineStr">
+      <c r="DO18" t="inlineStr"/>
+      <c r="DP18" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP18" t="inlineStr">
+      <c r="DQ18" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ18" t="inlineStr">
+      <c r="DR18" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR18" t="inlineStr">
+      <c r="DS18" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS18" t="inlineStr">
+      <c r="DT18" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT18" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU18" t="inlineStr"/>
+      <c r="DU18" t="b">
+        <v>0</v>
+      </c>
       <c r="DV18" t="inlineStr"/>
       <c r="DW18" t="inlineStr"/>
-      <c r="DX18" t="inlineStr">
+      <c r="DX18" t="inlineStr"/>
+      <c r="DY18" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -6649,7 +6671,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6804,7 +6826,7 @@
       <c r="BO19" t="inlineStr"/>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ19" t="b">
@@ -6903,72 +6925,73 @@
       <c r="DD19" t="inlineStr"/>
       <c r="DE19" t="inlineStr"/>
       <c r="DF19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH19" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI19" t="n">
+      <c r="DI19" t="inlineStr"/>
+      <c r="DJ19" t="n">
         <v>18</v>
       </c>
-      <c r="DJ19" t="inlineStr">
+      <c r="DK19" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK19" t="inlineStr">
+      <c r="DL19" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL19" t="inlineStr">
+      <c r="DM19" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM19" t="inlineStr">
+      <c r="DN19" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN19" t="inlineStr"/>
-      <c r="DO19" t="inlineStr">
+      <c r="DO19" t="inlineStr"/>
+      <c r="DP19" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP19" t="inlineStr">
+      <c r="DQ19" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ19" t="inlineStr">
+      <c r="DR19" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR19" t="inlineStr">
+      <c r="DS19" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS19" t="inlineStr">
+      <c r="DT19" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT19" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU19" t="inlineStr"/>
+      <c r="DU19" t="b">
+        <v>0</v>
+      </c>
       <c r="DV19" t="inlineStr"/>
       <c r="DW19" t="inlineStr"/>
-      <c r="DX19" t="inlineStr">
+      <c r="DX19" t="inlineStr"/>
+      <c r="DY19" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -6977,7 +7000,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7132,7 +7155,7 @@
       <c r="BO20" t="inlineStr"/>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ20" t="b">
@@ -7231,72 +7254,73 @@
       <c r="DD20" t="inlineStr"/>
       <c r="DE20" t="inlineStr"/>
       <c r="DF20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH20" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI20" t="n">
+      <c r="DI20" t="inlineStr"/>
+      <c r="DJ20" t="n">
         <v>19</v>
       </c>
-      <c r="DJ20" t="inlineStr">
+      <c r="DK20" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK20" t="inlineStr">
+      <c r="DL20" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL20" t="inlineStr">
+      <c r="DM20" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM20" t="inlineStr">
+      <c r="DN20" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN20" t="inlineStr"/>
-      <c r="DO20" t="inlineStr">
+      <c r="DO20" t="inlineStr"/>
+      <c r="DP20" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP20" t="inlineStr">
+      <c r="DQ20" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ20" t="inlineStr">
+      <c r="DR20" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR20" t="inlineStr">
+      <c r="DS20" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS20" t="inlineStr">
+      <c r="DT20" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT20" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU20" t="inlineStr"/>
+      <c r="DU20" t="b">
+        <v>0</v>
+      </c>
       <c r="DV20" t="inlineStr"/>
       <c r="DW20" t="inlineStr"/>
-      <c r="DX20" t="inlineStr">
+      <c r="DX20" t="inlineStr"/>
+      <c r="DY20" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -7305,7 +7329,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7460,7 +7484,7 @@
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ21" t="b">
@@ -7559,72 +7583,73 @@
       <c r="DD21" t="inlineStr"/>
       <c r="DE21" t="inlineStr"/>
       <c r="DF21" t="n">
+        <v>23</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>23</v>
+      </c>
+      <c r="DH21" t="inlineStr">
+        <is>
+          <t>trend=50; relative_strength=50; liquidity=50</t>
+        </is>
+      </c>
+      <c r="DI21" t="inlineStr"/>
+      <c r="DJ21" t="n">
         <v>20</v>
       </c>
-      <c r="DG21" t="n">
-        <v>20</v>
-      </c>
-      <c r="DH21" t="inlineStr">
-        <is>
-          <t>trend=50; relative_strength=50; liquidity=50</t>
-        </is>
-      </c>
-      <c r="DI21" t="n">
-        <v>20</v>
-      </c>
-      <c r="DJ21" t="inlineStr">
+      <c r="DK21" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK21" t="inlineStr">
+      <c r="DL21" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL21" t="inlineStr">
+      <c r="DM21" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM21" t="inlineStr">
+      <c r="DN21" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN21" t="inlineStr"/>
-      <c r="DO21" t="inlineStr">
+      <c r="DO21" t="inlineStr"/>
+      <c r="DP21" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP21" t="inlineStr">
+      <c r="DQ21" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ21" t="inlineStr">
+      <c r="DR21" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR21" t="inlineStr">
+      <c r="DS21" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS21" t="inlineStr">
+      <c r="DT21" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT21" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU21" t="inlineStr"/>
+      <c r="DU21" t="b">
+        <v>0</v>
+      </c>
       <c r="DV21" t="inlineStr"/>
       <c r="DW21" t="inlineStr"/>
-      <c r="DX21" t="inlineStr">
+      <c r="DX21" t="inlineStr"/>
+      <c r="DY21" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -7788,7 +7813,7 @@
       <c r="BO22" t="inlineStr"/>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ22" t="b">
@@ -7887,72 +7912,73 @@
       <c r="DD22" t="inlineStr"/>
       <c r="DE22" t="inlineStr"/>
       <c r="DF22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH22" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI22" t="n">
+      <c r="DI22" t="inlineStr"/>
+      <c r="DJ22" t="n">
         <v>21</v>
       </c>
-      <c r="DJ22" t="inlineStr">
+      <c r="DK22" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK22" t="inlineStr">
+      <c r="DL22" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL22" t="inlineStr">
+      <c r="DM22" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM22" t="inlineStr">
+      <c r="DN22" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN22" t="inlineStr"/>
-      <c r="DO22" t="inlineStr">
+      <c r="DO22" t="inlineStr"/>
+      <c r="DP22" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP22" t="inlineStr">
+      <c r="DQ22" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ22" t="inlineStr">
+      <c r="DR22" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR22" t="inlineStr">
+      <c r="DS22" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS22" t="inlineStr">
+      <c r="DT22" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT22" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU22" t="inlineStr"/>
+      <c r="DU22" t="b">
+        <v>0</v>
+      </c>
       <c r="DV22" t="inlineStr"/>
       <c r="DW22" t="inlineStr"/>
-      <c r="DX22" t="inlineStr">
+      <c r="DX22" t="inlineStr"/>
+      <c r="DY22" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -7961,7 +7987,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8116,7 +8142,7 @@
       <c r="BO23" t="inlineStr"/>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ23" t="b">
@@ -8215,72 +8241,73 @@
       <c r="DD23" t="inlineStr"/>
       <c r="DE23" t="inlineStr"/>
       <c r="DF23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH23" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI23" t="n">
+      <c r="DI23" t="inlineStr"/>
+      <c r="DJ23" t="n">
         <v>22</v>
       </c>
-      <c r="DJ23" t="inlineStr">
+      <c r="DK23" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK23" t="inlineStr">
+      <c r="DL23" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL23" t="inlineStr">
+      <c r="DM23" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM23" t="inlineStr">
+      <c r="DN23" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN23" t="inlineStr"/>
-      <c r="DO23" t="inlineStr">
+      <c r="DO23" t="inlineStr"/>
+      <c r="DP23" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP23" t="inlineStr">
+      <c r="DQ23" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ23" t="inlineStr">
+      <c r="DR23" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR23" t="inlineStr">
+      <c r="DS23" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS23" t="inlineStr">
+      <c r="DT23" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT23" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU23" t="inlineStr"/>
+      <c r="DU23" t="b">
+        <v>0</v>
+      </c>
       <c r="DV23" t="inlineStr"/>
       <c r="DW23" t="inlineStr"/>
-      <c r="DX23" t="inlineStr">
+      <c r="DX23" t="inlineStr"/>
+      <c r="DY23" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -8289,7 +8316,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8444,7 +8471,7 @@
       <c r="BO24" t="inlineStr"/>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ24" t="b">
@@ -8543,72 +8570,73 @@
       <c r="DD24" t="inlineStr"/>
       <c r="DE24" t="inlineStr"/>
       <c r="DF24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH24" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI24" t="n">
+      <c r="DI24" t="inlineStr"/>
+      <c r="DJ24" t="n">
         <v>23</v>
       </c>
-      <c r="DJ24" t="inlineStr">
+      <c r="DK24" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK24" t="inlineStr">
+      <c r="DL24" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL24" t="inlineStr">
+      <c r="DM24" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM24" t="inlineStr">
+      <c r="DN24" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN24" t="inlineStr"/>
-      <c r="DO24" t="inlineStr">
+      <c r="DO24" t="inlineStr"/>
+      <c r="DP24" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP24" t="inlineStr">
+      <c r="DQ24" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ24" t="inlineStr">
+      <c r="DR24" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR24" t="inlineStr">
+      <c r="DS24" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS24" t="inlineStr">
+      <c r="DT24" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT24" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU24" t="inlineStr"/>
+      <c r="DU24" t="b">
+        <v>0</v>
+      </c>
       <c r="DV24" t="inlineStr"/>
       <c r="DW24" t="inlineStr"/>
-      <c r="DX24" t="inlineStr">
+      <c r="DX24" t="inlineStr"/>
+      <c r="DY24" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -8617,7 +8645,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8772,7 +8800,7 @@
       <c r="BO25" t="inlineStr"/>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ25" t="b">
@@ -8871,72 +8899,73 @@
       <c r="DD25" t="inlineStr"/>
       <c r="DE25" t="inlineStr"/>
       <c r="DF25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH25" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI25" t="n">
+      <c r="DI25" t="inlineStr"/>
+      <c r="DJ25" t="n">
         <v>24</v>
       </c>
-      <c r="DJ25" t="inlineStr">
+      <c r="DK25" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK25" t="inlineStr">
+      <c r="DL25" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL25" t="inlineStr">
+      <c r="DM25" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM25" t="inlineStr">
+      <c r="DN25" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN25" t="inlineStr"/>
-      <c r="DO25" t="inlineStr">
+      <c r="DO25" t="inlineStr"/>
+      <c r="DP25" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP25" t="inlineStr">
+      <c r="DQ25" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ25" t="inlineStr">
+      <c r="DR25" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR25" t="inlineStr">
+      <c r="DS25" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS25" t="inlineStr">
+      <c r="DT25" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT25" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU25" t="inlineStr"/>
+      <c r="DU25" t="b">
+        <v>0</v>
+      </c>
       <c r="DV25" t="inlineStr"/>
       <c r="DW25" t="inlineStr"/>
-      <c r="DX25" t="inlineStr">
+      <c r="DX25" t="inlineStr"/>
+      <c r="DY25" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -8945,7 +8974,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9100,7 +9129,7 @@
       <c r="BO26" t="inlineStr"/>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ26" t="b">
@@ -9199,72 +9228,73 @@
       <c r="DD26" t="inlineStr"/>
       <c r="DE26" t="inlineStr"/>
       <c r="DF26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH26" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI26" t="n">
+      <c r="DI26" t="inlineStr"/>
+      <c r="DJ26" t="n">
         <v>25</v>
       </c>
-      <c r="DJ26" t="inlineStr">
+      <c r="DK26" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK26" t="inlineStr">
+      <c r="DL26" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL26" t="inlineStr">
+      <c r="DM26" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM26" t="inlineStr">
+      <c r="DN26" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN26" t="inlineStr"/>
-      <c r="DO26" t="inlineStr">
+      <c r="DO26" t="inlineStr"/>
+      <c r="DP26" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP26" t="inlineStr">
+      <c r="DQ26" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ26" t="inlineStr">
+      <c r="DR26" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR26" t="inlineStr">
+      <c r="DS26" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS26" t="inlineStr">
+      <c r="DT26" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT26" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU26" t="inlineStr"/>
+      <c r="DU26" t="b">
+        <v>0</v>
+      </c>
       <c r="DV26" t="inlineStr"/>
       <c r="DW26" t="inlineStr"/>
-      <c r="DX26" t="inlineStr">
+      <c r="DX26" t="inlineStr"/>
+      <c r="DY26" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
@@ -9273,7 +9303,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOXL</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9428,7 +9458,7 @@
       <c r="BO27" t="inlineStr"/>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>2026-08-01 10:27:31-04:00</t>
+          <t>2026-08-08 10:23:23-04:00</t>
         </is>
       </c>
       <c r="BQ27" t="b">
@@ -9527,72 +9557,73 @@
       <c r="DD27" t="inlineStr"/>
       <c r="DE27" t="inlineStr"/>
       <c r="DF27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DG27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="DH27" t="inlineStr">
         <is>
           <t>trend=50; relative_strength=50; liquidity=50</t>
         </is>
       </c>
-      <c r="DI27" t="n">
+      <c r="DI27" t="inlineStr"/>
+      <c r="DJ27" t="n">
         <v>26</v>
       </c>
-      <c r="DJ27" t="inlineStr">
+      <c r="DK27" t="inlineStr">
         <is>
           <t>INTRADAY</t>
         </is>
       </c>
-      <c r="DK27" t="inlineStr">
+      <c r="DL27" t="inlineStr">
         <is>
           <t>NO_RECOMMENDATION</t>
         </is>
       </c>
-      <c r="DL27" t="inlineStr">
+      <c r="DM27" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DM27" t="inlineStr">
+      <c r="DN27" t="inlineStr">
         <is>
           <t>NOT_REQUESTED</t>
         </is>
       </c>
-      <c r="DN27" t="inlineStr"/>
-      <c r="DO27" t="inlineStr">
+      <c r="DO27" t="inlineStr"/>
+      <c r="DP27" t="inlineStr">
         <is>
           <t>NOT_CREATED</t>
         </is>
       </c>
-      <c r="DP27" t="inlineStr">
+      <c r="DQ27" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DQ27" t="inlineStr">
+      <c r="DR27" t="inlineStr">
         <is>
           <t>NO_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DR27" t="inlineStr">
+      <c r="DS27" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DS27" t="inlineStr">
+      <c r="DT27" t="inlineStr">
         <is>
           <t>NOT_LIFECYCLE_EVENT</t>
         </is>
       </c>
-      <c r="DT27" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU27" t="inlineStr"/>
+      <c r="DU27" t="b">
+        <v>0</v>
+      </c>
       <c r="DV27" t="inlineStr"/>
       <c r="DW27" t="inlineStr"/>
-      <c r="DX27" t="inlineStr">
+      <c r="DX27" t="inlineStr"/>
+      <c r="DY27" t="inlineStr">
         <is>
           <t>LIFECYCLE_FILTER</t>
         </is>
